--- a/AllEventData.xlsx
+++ b/AllEventData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\Documents\GitHub\strewnlab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F060F69-143D-4DF2-A78E-99C29F0B4C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A87CD47-6E27-4637-9ACE-F57963EE8109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="645" yWindow="1800" windowWidth="23070" windowHeight="12825" xr2:uid="{C46C341C-A654-450D-9491-A8F495B2F4ED}"/>
+    <workbookView xWindow="11700" yWindow="990" windowWidth="21600" windowHeight="11385" xr2:uid="{C46C341C-A654-450D-9491-A8F495B2F4ED}"/>
   </bookViews>
   <sheets>
     <sheet name="AllEventData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
     <externalReference r:id="rId13"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AllEventData!$A$5:$BI$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AllEventData!$A$5:$BI$225</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Database!$A$1:$H$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Radar!$D$6:$M$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$A$5:$M$71</definedName>
@@ -209,7 +209,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3790" uniqueCount="2121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3806" uniqueCount="2125">
   <si>
     <t>UTC Date and Time</t>
   </si>
@@ -6404,9 +6404,6 @@
     <t>North Carolina</t>
   </si>
   <si>
-    <t>Luzon</t>
-  </si>
-  <si>
     <t>Tuguegarao</t>
   </si>
   <si>
@@ -6573,6 +6570,21 @@
   </si>
   <si>
     <t>Rede</t>
+  </si>
+  <si>
+    <t>Scotland</t>
+  </si>
+  <si>
+    <t>Loch Treig</t>
+  </si>
+  <si>
+    <t>Fersit</t>
+  </si>
+  <si>
+    <t>2024 RW1</t>
+  </si>
+  <si>
+    <t>Blackville</t>
   </si>
 </sst>
 </file>
@@ -16820,7 +16832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{332638A7-5364-4539-88F3-B010BD503402}">
-  <dimension ref="A1:BI224"/>
+  <dimension ref="A1:BI226"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="6" customWidth="1"/>
@@ -20622,7 +20634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>20</v>
       </c>
@@ -47854,7 +47866,7 @@
         <v>71000</v>
       </c>
       <c r="K195" s="3">
-        <f t="shared" ref="K195:K218" si="17">I195*J195^2/2/4.184/10^12</f>
+        <f t="shared" ref="K195:K226" si="17">I195*J195^2/2/4.184/10^12</f>
         <v>1.2048279158699809E-3</v>
       </c>
       <c r="L195" s="3">
@@ -51232,13 +51244,13 @@
         <v>212</v>
       </c>
       <c r="B213" s="6" t="s">
+        <v>2123</v>
+      </c>
+      <c r="C213" s="6" t="s">
         <v>2064</v>
       </c>
-      <c r="C213" s="6" t="s">
+      <c r="D213" s="6" t="s">
         <v>2065</v>
-      </c>
-      <c r="D213" s="6" t="s">
-        <v>2066</v>
       </c>
       <c r="E213" s="6" t="s">
         <v>1456</v>
@@ -51422,10 +51434,10 @@
         <v>213</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="D214" s="6" t="s">
         <v>56</v>
@@ -51611,10 +51623,10 @@
         <v>214</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="D215" s="6" t="s">
         <v>58</v>
@@ -51802,13 +51814,13 @@
         <v>215</v>
       </c>
       <c r="B216" s="6" t="s">
+        <v>2069</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>2069</v>
+      </c>
+      <c r="D216" s="6" t="s">
         <v>2070</v>
-      </c>
-      <c r="C216" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D216" s="6" t="s">
-        <v>2071</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>4</v>
@@ -51981,7 +51993,7 @@
         <v>3</v>
       </c>
       <c r="BH216" s="40" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="BI216" s="40">
         <v>0</v>
@@ -51992,10 +52004,10 @@
         <v>216</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="D217" s="6" t="s">
         <v>154</v>
@@ -52171,7 +52183,7 @@
         <v>2</v>
       </c>
       <c r="BH217" s="40" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="BI217" s="40">
         <v>0</v>
@@ -52182,10 +52194,10 @@
         <v>217</v>
       </c>
       <c r="B218" s="6" t="s">
+        <v>2090</v>
+      </c>
+      <c r="C218" s="6" t="s">
         <v>2091</v>
-      </c>
-      <c r="C218" s="6" t="s">
-        <v>2092</v>
       </c>
       <c r="D218" s="6" t="s">
         <v>1585</v>
@@ -52372,13 +52384,13 @@
         <v>218</v>
       </c>
       <c r="B219" s="6" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C219" s="6" t="s">
+        <v>2106</v>
+      </c>
+      <c r="D219" s="6" t="s">
         <v>2107</v>
-      </c>
-      <c r="C219" s="6" t="s">
-        <v>2107</v>
-      </c>
-      <c r="D219" s="6" t="s">
-        <v>2108</v>
       </c>
       <c r="E219" s="6" t="s">
         <v>4</v>
@@ -52400,6 +52412,7 @@
         <v>13357.343371912368</v>
       </c>
       <c r="K219" s="3">
+        <f t="shared" si="17"/>
         <v>2.1321537040531937E-3</v>
       </c>
       <c r="L219" s="3">
@@ -52547,7 +52560,7 @@
         <v>1</v>
       </c>
       <c r="BH219" s="40" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="BI219" s="40">
         <v>0</v>
@@ -52558,13 +52571,13 @@
         <v>219</v>
       </c>
       <c r="B220" s="6" t="s">
+        <v>2109</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>2109</v>
+      </c>
+      <c r="D220" s="6" t="s">
         <v>2110</v>
-      </c>
-      <c r="C220" s="6" t="s">
-        <v>2110</v>
-      </c>
-      <c r="D220" s="6" t="s">
-        <v>2111</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>4</v>
@@ -52586,6 +52599,7 @@
         <v>13198.002849754146</v>
       </c>
       <c r="K220" s="3">
+        <f t="shared" si="17"/>
         <v>2.0815879448149925E-3</v>
       </c>
       <c r="L220" s="3">
@@ -52733,7 +52747,7 @@
         <v>1</v>
       </c>
       <c r="BH220" s="40" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="BI220" s="40">
         <v>0</v>
@@ -52744,10 +52758,10 @@
         <v>220</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="D221" s="6" t="s">
         <v>1504</v>
@@ -52762,7 +52776,7 @@
         <v>-6</v>
       </c>
       <c r="H221" s="4">
-        <f t="shared" ref="H221:H224" si="20">F221+G221/24</f>
+        <f t="shared" ref="H221:H226" si="20">F221+G221/24</f>
         <v>45798.115381944444</v>
       </c>
       <c r="I221" s="3">
@@ -52772,7 +52786,8 @@
         <v>15000</v>
       </c>
       <c r="K221" s="3">
-        <v>2.0815879448149925E-3</v>
+        <f t="shared" si="17"/>
+        <v>2.6888145315487571E-3</v>
       </c>
       <c r="L221" s="3">
         <v>235.12</v>
@@ -52800,7 +52815,7 @@
         <v>5000</v>
       </c>
       <c r="T221" s="3">
-        <f>M221</f>
+        <f t="shared" ref="T221:T226" si="21">M221</f>
         <v>69.236000000000004</v>
       </c>
       <c r="U221" s="3">
@@ -52922,7 +52937,7 @@
         <v>1</v>
       </c>
       <c r="BH221" s="40" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="BI221" s="40">
         <v>0</v>
@@ -52933,10 +52948,10 @@
         <v>221</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="D222" s="6" t="s">
         <v>1321</v>
@@ -52961,7 +52976,8 @@
         <v>20000</v>
       </c>
       <c r="K222" s="3">
-        <v>2.0815879448149925E-3</v>
+        <f t="shared" si="17"/>
+        <v>2.3900573613766726E-3</v>
       </c>
       <c r="L222" s="3">
         <v>21.524999999999999</v>
@@ -52989,7 +53005,7 @@
         <v>5000</v>
       </c>
       <c r="T222" s="3">
-        <f>M222</f>
+        <f t="shared" si="21"/>
         <v>62.933999999999997</v>
       </c>
       <c r="U222" s="3">
@@ -53111,7 +53127,7 @@
         <v>1</v>
       </c>
       <c r="BH222" s="40" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="BI222" s="40">
         <v>0</v>
@@ -53122,13 +53138,13 @@
         <v>222</v>
       </c>
       <c r="B223" s="6" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>2116</v>
+      </c>
+      <c r="D223" s="6" t="s">
         <v>2117</v>
-      </c>
-      <c r="C223" s="6" t="s">
-        <v>2117</v>
-      </c>
-      <c r="D223" s="6" t="s">
-        <v>2118</v>
       </c>
       <c r="E223" s="6" t="s">
         <v>418</v>
@@ -53150,7 +53166,8 @@
         <v>15000</v>
       </c>
       <c r="K223" s="3">
-        <v>2.0815879448149925E-3</v>
+        <f t="shared" si="17"/>
+        <v>2.6888145315487572E-2</v>
       </c>
       <c r="L223" s="3">
         <v>355</v>
@@ -53177,7 +53194,7 @@
         <v>5000</v>
       </c>
       <c r="T223" s="3">
-        <f>M223</f>
+        <f t="shared" si="21"/>
         <v>55</v>
       </c>
       <c r="U223" s="3">
@@ -53298,7 +53315,7 @@
         <v>2</v>
       </c>
       <c r="BH223" s="40" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="BI223" s="40">
         <v>0</v>
@@ -53309,10 +53326,10 @@
         <v>223</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="D224" s="6" t="s">
         <v>1434</v>
@@ -53337,7 +53354,8 @@
         <v>11719</v>
       </c>
       <c r="K224" s="3">
-        <v>2.0815879448149925E-3</v>
+        <f t="shared" si="17"/>
+        <v>1.6411921725621415E-5</v>
       </c>
       <c r="L224" s="3">
         <v>322.75729999999999</v>
@@ -53365,7 +53383,7 @@
         <v>1500</v>
       </c>
       <c r="T224" s="3">
-        <f>M224</f>
+        <f t="shared" si="21"/>
         <v>67.229100000000003</v>
       </c>
       <c r="U224" s="3">
@@ -53457,7 +53475,7 @@
         <v>0</v>
       </c>
       <c r="AX224" s="38">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="AY224" s="38">
         <v>0</v>
@@ -53493,8 +53511,387 @@
         <v>0</v>
       </c>
     </row>
+    <row r="225" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A225" s="6">
+        <v>224</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D225" s="6" t="s">
+        <v>2120</v>
+      </c>
+      <c r="E225" s="6" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F225" s="17">
+        <v>45840.993113425924</v>
+      </c>
+      <c r="G225" s="21">
+        <v>0</v>
+      </c>
+      <c r="H225" s="4">
+        <f t="shared" si="20"/>
+        <v>45840.993113425924</v>
+      </c>
+      <c r="I225" s="3">
+        <v>61</v>
+      </c>
+      <c r="J225" s="3">
+        <v>12119.68</v>
+      </c>
+      <c r="K225" s="3">
+        <f t="shared" si="17"/>
+        <v>1.0707558844940727E-3</v>
+      </c>
+      <c r="L225" s="3">
+        <v>85.263199999999998</v>
+      </c>
+      <c r="M225" s="3">
+        <v>59.543700000000001</v>
+      </c>
+      <c r="N225" s="3" t="s">
+        <v>1329</v>
+      </c>
+      <c r="O225" s="3">
+        <v>56.808013000000003</v>
+      </c>
+      <c r="P225" s="3">
+        <v>-4.7710189999999999</v>
+      </c>
+      <c r="Q225" s="3">
+        <v>24686.42</v>
+      </c>
+      <c r="R225" s="3">
+        <f>Q225</f>
+        <v>24686.42</v>
+      </c>
+      <c r="S225" s="3">
+        <v>8000</v>
+      </c>
+      <c r="T225" s="3">
+        <f t="shared" si="21"/>
+        <v>59.543700000000001</v>
+      </c>
+      <c r="U225" s="3">
+        <f>Q225</f>
+        <v>24686.42</v>
+      </c>
+      <c r="V225" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="W225" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="X225" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y225" s="3">
+        <v>60000</v>
+      </c>
+      <c r="Z225" s="3">
+        <v>60000</v>
+      </c>
+      <c r="AA225" s="5">
+        <v>1.46</v>
+      </c>
+      <c r="AB225" s="5">
+        <v>0.151</v>
+      </c>
+      <c r="AC225" s="5">
+        <v>0.129</v>
+      </c>
+      <c r="AD225" s="5">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="AE225" s="5">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="AF225" s="5">
+        <v>500</v>
+      </c>
+      <c r="AG225" s="5">
+        <v>-1</v>
+      </c>
+      <c r="AH225" s="5">
+        <v>1</v>
+      </c>
+      <c r="AI225" s="45">
+        <v>0</v>
+      </c>
+      <c r="AJ225" s="45">
+        <v>0</v>
+      </c>
+      <c r="AK225" s="45">
+        <v>0</v>
+      </c>
+      <c r="AL225" s="23">
+        <v>0</v>
+      </c>
+      <c r="AM225" s="23">
+        <v>0</v>
+      </c>
+      <c r="AN225" s="23">
+        <v>0</v>
+      </c>
+      <c r="AO225" s="23">
+        <v>0</v>
+      </c>
+      <c r="AP225" s="23">
+        <v>0</v>
+      </c>
+      <c r="AQ225" s="23">
+        <v>0</v>
+      </c>
+      <c r="AR225" s="25">
+        <v>0</v>
+      </c>
+      <c r="AS225" s="52">
+        <v>0</v>
+      </c>
+      <c r="AT225" s="50">
+        <v>0</v>
+      </c>
+      <c r="AU225" s="50">
+        <v>0</v>
+      </c>
+      <c r="AV225" s="50">
+        <v>0</v>
+      </c>
+      <c r="AW225" s="38">
+        <v>0</v>
+      </c>
+      <c r="AX225" s="38">
+        <v>135</v>
+      </c>
+      <c r="AY225" s="38">
+        <v>0</v>
+      </c>
+      <c r="AZ225" s="38">
+        <v>0</v>
+      </c>
+      <c r="BA225" s="38">
+        <v>0</v>
+      </c>
+      <c r="BB225" s="38">
+        <v>0</v>
+      </c>
+      <c r="BC225" s="38">
+        <v>0</v>
+      </c>
+      <c r="BD225" s="38">
+        <v>0</v>
+      </c>
+      <c r="BE225" s="38">
+        <v>0</v>
+      </c>
+      <c r="BF225" s="38">
+        <v>0</v>
+      </c>
+      <c r="BG225" s="40">
+        <v>4</v>
+      </c>
+      <c r="BH225" s="40" t="s">
+        <v>1433</v>
+      </c>
+      <c r="BI225" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A226" s="6">
+        <v>225</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>2124</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>2124</v>
+      </c>
+      <c r="D226" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="E226" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F226" s="17">
+        <v>45834.683993055558</v>
+      </c>
+      <c r="G226" s="21">
+        <v>-4</v>
+      </c>
+      <c r="H226" s="4">
+        <f t="shared" si="20"/>
+        <v>45834.517326388894</v>
+      </c>
+      <c r="I226" s="3">
+        <v>1727</v>
+      </c>
+      <c r="J226" s="3">
+        <v>18000</v>
+      </c>
+      <c r="K226" s="3">
+        <f t="shared" si="17"/>
+        <v>6.6867590822179732E-2</v>
+      </c>
+      <c r="L226" s="3">
+        <v>265.8</v>
+      </c>
+      <c r="M226" s="3">
+        <v>25</v>
+      </c>
+      <c r="N226" s="3" t="s">
+        <v>1329</v>
+      </c>
+      <c r="O226" s="3">
+        <v>33.398569000000002</v>
+      </c>
+      <c r="P226" s="3">
+        <v>-84.102630000000005</v>
+      </c>
+      <c r="Q226" s="3">
+        <v>32600</v>
+      </c>
+      <c r="R226" s="3">
+        <f>Q226</f>
+        <v>32600</v>
+      </c>
+      <c r="S226" s="3">
+        <v>8000</v>
+      </c>
+      <c r="T226" s="3">
+        <f t="shared" si="21"/>
+        <v>25</v>
+      </c>
+      <c r="U226" s="3">
+        <v>23000</v>
+      </c>
+      <c r="V226" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="W226" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="X226" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y226" s="3">
+        <v>60000</v>
+      </c>
+      <c r="Z226" s="3">
+        <v>60000</v>
+      </c>
+      <c r="AA226" s="5">
+        <v>5000</v>
+      </c>
+      <c r="AB226" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC226" s="5">
+        <v>5</v>
+      </c>
+      <c r="AD226" s="5">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AE226" s="5">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AF226" s="5">
+        <v>500</v>
+      </c>
+      <c r="AG226" s="5">
+        <v>-1</v>
+      </c>
+      <c r="AH226" s="5">
+        <v>1</v>
+      </c>
+      <c r="AI226" s="45">
+        <v>0</v>
+      </c>
+      <c r="AJ226" s="45">
+        <v>0</v>
+      </c>
+      <c r="AK226" s="45">
+        <v>0</v>
+      </c>
+      <c r="AL226" s="23">
+        <v>0</v>
+      </c>
+      <c r="AM226" s="23">
+        <v>50</v>
+      </c>
+      <c r="AN226" s="23">
+        <v>0</v>
+      </c>
+      <c r="AO226" s="23">
+        <v>0</v>
+      </c>
+      <c r="AP226" s="23">
+        <v>0</v>
+      </c>
+      <c r="AQ226" s="23">
+        <v>0</v>
+      </c>
+      <c r="AR226" s="25">
+        <v>0</v>
+      </c>
+      <c r="AS226" s="52">
+        <v>0</v>
+      </c>
+      <c r="AT226" s="50">
+        <v>0</v>
+      </c>
+      <c r="AU226" s="50">
+        <v>0</v>
+      </c>
+      <c r="AV226" s="50">
+        <v>0</v>
+      </c>
+      <c r="AW226" s="38">
+        <v>0</v>
+      </c>
+      <c r="AX226" s="38">
+        <v>4</v>
+      </c>
+      <c r="AY226" s="38">
+        <v>0</v>
+      </c>
+      <c r="AZ226" s="38">
+        <v>0</v>
+      </c>
+      <c r="BA226" s="38">
+        <v>0</v>
+      </c>
+      <c r="BB226" s="38">
+        <v>0</v>
+      </c>
+      <c r="BC226" s="38">
+        <v>0</v>
+      </c>
+      <c r="BD226" s="38">
+        <v>0</v>
+      </c>
+      <c r="BE226" s="38">
+        <v>0</v>
+      </c>
+      <c r="BF226" s="38">
+        <v>0</v>
+      </c>
+      <c r="BG226" s="40">
+        <v>4</v>
+      </c>
+      <c r="BH226" s="40" t="s">
+        <v>2038</v>
+      </c>
+      <c r="BI226" s="40">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:BI216" xr:uid="{332638A7-5364-4539-88F3-B010BD503402}"/>
+  <autoFilter ref="A5:BI225" xr:uid="{332638A7-5364-4539-88F3-B010BD503402}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -56304,17 +56701,17 @@
     <row r="2" spans="1:61" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="53">
         <f>MAX(AllEventData!A:A)+1</f>
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="C2" s="53" t="str">
         <f>B2</f>
         <v>Atlantic</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>4</v>
@@ -56494,7 +56891,7 @@
         <v>1</v>
       </c>
       <c r="BH2" s="16" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="BI2" s="16">
         <v>0</v>
@@ -56502,14 +56899,14 @@
     </row>
     <row r="5" spans="1:61" ht="23.25" x14ac:dyDescent="0.35">
       <c r="H5" s="62" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="I5" s="63"/>
       <c r="J5" s="64"/>
     </row>
     <row r="6" spans="1:61" x14ac:dyDescent="0.25">
       <c r="E6" s="59" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="F6" s="59" t="s">
         <v>155</v>
@@ -56519,7 +56916,7 @@
     </row>
     <row r="7" spans="1:61" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="E7" s="60">
         <v>41.178705000000001</v>
@@ -56528,14 +56925,14 @@
         <v>41.344289000000003</v>
       </c>
       <c r="H7" s="67" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="I7" s="68"/>
       <c r="J7" s="66"/>
     </row>
     <row r="8" spans="1:61" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="E8" s="60">
         <v>-95.095505000000003</v>
@@ -56544,7 +56941,7 @@
         <v>-95.067105999999995</v>
       </c>
       <c r="H8" s="69" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="I8" s="15">
         <v>45</v>
@@ -56553,7 +56950,7 @@
     </row>
     <row r="9" spans="1:61" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="E9" s="60">
         <v>80</v>
@@ -56562,7 +56959,7 @@
         <v>23.585000000000001</v>
       </c>
       <c r="H9" s="69" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="I9" s="16">
         <f>0.094*I8 + 19.355</f>
@@ -56584,17 +56981,17 @@
     </row>
     <row r="12" spans="1:61" x14ac:dyDescent="0.25">
       <c r="E12" s="33" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="F12" s="33" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="H12" s="65"/>
       <c r="J12" s="66"/>
     </row>
     <row r="13" spans="1:61" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="E13" s="61">
         <f>DEGREES(ATAN(E17/(E9-F9)))</f>
@@ -56606,7 +57003,7 @@
     </row>
     <row r="14" spans="1:61" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="E14" s="60">
         <v>4.5</v>
@@ -56619,7 +57016,7 @@
     </row>
     <row r="15" spans="1:61" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="E15" s="61">
         <f>MOD(DEGREES(ATAN2(COS(RADIANS(E7))*SIN(RADIANS(F7))-SIN(RADIANS(E7))*COS(RADIANS(F7))*COS(RADIANS(F8-E8)),SIN(RADIANS(F8-E8))*COS(RADIANS(F7)))),360)</f>
@@ -56631,7 +57028,7 @@
     </row>
     <row r="16" spans="1:61" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="E16" s="61">
         <f>ACOS(COS(RADIANS(90-E7)) * COS(RADIANS(90-F7)) + SIN(RADIANS(90-E7)) * SIN(RADIANS(90-F7)) * COS(RADIANS(E8-F8))) * 6371</f>
@@ -56643,7 +57040,7 @@
     </row>
     <row r="17" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D17" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="E17" s="58">
         <f>SQRT((E9-F9)^2+E16^2)</f>
@@ -56657,7 +57054,7 @@
     </row>
     <row r="18" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D18" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="E18" s="58">
         <f>E17/E14</f>
@@ -56725,7 +57122,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="B2" s="12">
         <f t="shared" ref="B2:M2" si="0">AVERAGE(B6:B71)</f>
@@ -56778,7 +57175,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="B3" s="12">
         <f t="shared" ref="B3:M3" si="1">STDEV(B6:B71)</f>
@@ -59702,7 +60099,7 @@
         <v>408</v>
       </c>
       <c r="M7">
-        <v>8.5</v>
+        <v>1.6</v>
       </c>
       <c r="Q7" t="s">
         <v>13</v>
@@ -59730,7 +60127,7 @@
       </c>
       <c r="M8">
         <f>J13/M7</f>
-        <v>9.9826839696924363</v>
+        <v>39.705950435671475</v>
       </c>
       <c r="N8" t="s">
         <v>2041</v>
@@ -59786,11 +60183,11 @@
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="H11" s="16">
         <f>DEGREES(ATAN(J20/F15))</f>
-        <v>45</v>
+        <v>28.178590109959174</v>
       </c>
       <c r="J11">
         <f>90-H11</f>
-        <v>45</v>
+        <v>61.821409890040826</v>
       </c>
       <c r="N11">
         <v>18980</v>
@@ -59810,7 +60207,7 @@
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="J13" s="16">
         <f>SQRT(F15^2+J20^2)</f>
-        <v>84.852813742385706</v>
+        <v>63.529520697074361</v>
       </c>
       <c r="L13" t="e">
         <f>J13/L12</f>
@@ -59840,13 +60237,13 @@
       </c>
       <c r="F15" s="16">
         <f>F12-F18</f>
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="M16">
         <f>90-H11</f>
-        <v>45</v>
+        <v>61.821409890040826</v>
       </c>
     </row>
     <row r="18" spans="3:14" x14ac:dyDescent="0.25">
@@ -59854,7 +60251,7 @@
         <v>88</v>
       </c>
       <c r="F18" s="15">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="3:14" x14ac:dyDescent="0.25">
@@ -59862,11 +60259,11 @@
         <v>85</v>
       </c>
       <c r="J20" s="15">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N20">
         <f>8/COS(RADIANS(H11))</f>
-        <v>11.313708498984759</v>
+        <v>9.0756458138677658</v>
       </c>
     </row>
     <row r="21" spans="3:14" x14ac:dyDescent="0.25">
@@ -60137,44 +60534,44 @@
   <sheetData>
     <row r="2" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D2" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="E2" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="3" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="E3" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="6" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="E6" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="F6" t="s">
         <v>122</v>
       </c>
       <c r="G6" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="H6" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="I6" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="K6" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="M6" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="7" spans="3:13" x14ac:dyDescent="0.25">
@@ -60182,7 +60579,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="8" spans="3:13" x14ac:dyDescent="0.25">
@@ -60190,13 +60587,13 @@
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="I8">
         <v>5</v>
@@ -60218,16 +60615,16 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="H9" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="I9">
         <v>4.2</v>
@@ -60246,19 +60643,19 @@
     </row>
     <row r="10" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="D10">
         <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="F10">
         <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="I10">
         <v>6</v>
@@ -60283,16 +60680,16 @@
         <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="F11">
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="H11" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="12" spans="3:13" x14ac:dyDescent="0.25">
@@ -60300,16 +60697,16 @@
         <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="F12">
         <v>19</v>
       </c>
       <c r="G12" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="H12" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="I12">
         <v>10</v>
@@ -60336,16 +60733,16 @@
         <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="F14">
         <v>7</v>
       </c>
       <c r="G14" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="H14" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="15" spans="3:13" x14ac:dyDescent="0.25">
@@ -60353,7 +60750,7 @@
         <v>112</v>
       </c>
       <c r="H15" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="I15">
         <v>5.6</v>
@@ -60372,13 +60769,13 @@
     </row>
     <row r="16" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="D16">
         <v>121</v>
       </c>
       <c r="H16" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="I16">
         <v>5.75</v>
@@ -60400,7 +60797,7 @@
         <v>211</v>
       </c>
       <c r="H17" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="I17">
         <v>5</v>
@@ -60422,16 +60819,16 @@
         <v>212</v>
       </c>
       <c r="E18" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="F18">
         <v>4</v>
       </c>
       <c r="G18" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="H18" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="I18">
         <v>4.75</v>
@@ -60453,13 +60850,13 @@
         <v>215</v>
       </c>
       <c r="E19" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="F19">
         <v>8</v>
       </c>
       <c r="H19" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="I19">
         <v>6</v>
@@ -60478,19 +60875,19 @@
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="D20">
         <v>221</v>
       </c>
       <c r="E20" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="F20">
         <v>2</v>
       </c>
       <c r="H20" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="I20">
         <v>6</v>

--- a/AllEventData.xlsx
+++ b/AllEventData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\Documents\GitHub\strewnlab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A87CD47-6E27-4637-9ACE-F57963EE8109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649AEC22-EA8F-4F13-B5E6-88094820B76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11700" yWindow="990" windowWidth="21600" windowHeight="11385" xr2:uid="{C46C341C-A654-450D-9491-A8F495B2F4ED}"/>
+    <workbookView xWindow="9195" yWindow="945" windowWidth="14670" windowHeight="12885" xr2:uid="{C46C341C-A654-450D-9491-A8F495B2F4ED}"/>
   </bookViews>
   <sheets>
     <sheet name="AllEventData" sheetId="1" r:id="rId1"/>
@@ -209,7 +209,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3806" uniqueCount="2125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="2126">
   <si>
     <t>UTC Date and Time</t>
   </si>
@@ -6585,6 +6585,9 @@
   </si>
   <si>
     <t>Blackville</t>
+  </si>
+  <si>
+    <t>Batchewana</t>
   </si>
 </sst>
 </file>
@@ -7817,6 +7820,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7824,7 +7828,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8197,6 +8200,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8204,7 +8208,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8581,6 +8584,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8588,7 +8592,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8931,6 +8934,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8938,7 +8942,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9328,6 +9331,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9335,7 +9339,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9797,6 +9800,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9804,7 +9808,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -12253,6 +12256,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -12260,7 +12264,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -16832,7 +16835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{332638A7-5364-4539-88F3-B010BD503402}">
-  <dimension ref="A1:BI226"/>
+  <dimension ref="A1:BI227"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="6" customWidth="1"/>
@@ -47866,7 +47869,7 @@
         <v>71000</v>
       </c>
       <c r="K195" s="3">
-        <f t="shared" ref="K195:K226" si="17">I195*J195^2/2/4.184/10^12</f>
+        <f t="shared" ref="K195:K227" si="17">I195*J195^2/2/4.184/10^12</f>
         <v>1.2048279158699809E-3</v>
       </c>
       <c r="L195" s="3">
@@ -52776,7 +52779,7 @@
         <v>-6</v>
       </c>
       <c r="H221" s="4">
-        <f t="shared" ref="H221:H226" si="20">F221+G221/24</f>
+        <f t="shared" ref="H221:H227" si="20">F221+G221/24</f>
         <v>45798.115381944444</v>
       </c>
       <c r="I221" s="3">
@@ -52815,7 +52818,7 @@
         <v>5000</v>
       </c>
       <c r="T221" s="3">
-        <f t="shared" ref="T221:T226" si="21">M221</f>
+        <f t="shared" ref="T221:T227" si="21">M221</f>
         <v>69.236000000000004</v>
       </c>
       <c r="U221" s="3">
@@ -53887,6 +53890,194 @@
         <v>2038</v>
       </c>
       <c r="BI226" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A227" s="6">
+        <v>226</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>2125</v>
+      </c>
+      <c r="C227" s="6" t="s">
+        <v>2125</v>
+      </c>
+      <c r="D227" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E227" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F227" s="17">
+        <v>45965.127349537041</v>
+      </c>
+      <c r="G227" s="21">
+        <v>-5</v>
+      </c>
+      <c r="H227" s="4">
+        <f t="shared" si="20"/>
+        <v>45964.919016203705</v>
+      </c>
+      <c r="I227" s="3">
+        <v>100</v>
+      </c>
+      <c r="J227" s="3">
+        <v>29000</v>
+      </c>
+      <c r="K227" s="3">
+        <f t="shared" si="17"/>
+        <v>1.0050191204588908E-2</v>
+      </c>
+      <c r="L227" s="3">
+        <v>311</v>
+      </c>
+      <c r="M227" s="3">
+        <v>60</v>
+      </c>
+      <c r="N227" s="3" t="s">
+        <v>1329</v>
+      </c>
+      <c r="O227" s="3">
+        <v>47.500999999999998</v>
+      </c>
+      <c r="P227" s="3">
+        <v>-84.072000000000003</v>
+      </c>
+      <c r="Q227" s="3">
+        <v>20000</v>
+      </c>
+      <c r="R227" s="3">
+        <f>Q227</f>
+        <v>20000</v>
+      </c>
+      <c r="S227" s="3">
+        <v>8000</v>
+      </c>
+      <c r="T227" s="3">
+        <v>63</v>
+      </c>
+      <c r="U227" s="3">
+        <v>30000</v>
+      </c>
+      <c r="V227" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="W227" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="X227" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y227" s="3">
+        <v>60000</v>
+      </c>
+      <c r="Z227" s="3">
+        <v>60000</v>
+      </c>
+      <c r="AA227" s="5">
+        <v>4000</v>
+      </c>
+      <c r="AB227" s="5">
+        <v>2</v>
+      </c>
+      <c r="AC227" s="5">
+        <v>3</v>
+      </c>
+      <c r="AD227" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE227" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF227" s="5">
+        <v>5000</v>
+      </c>
+      <c r="AG227" s="5">
+        <v>-1</v>
+      </c>
+      <c r="AH227" s="5">
+        <v>1</v>
+      </c>
+      <c r="AI227" s="45">
+        <v>0</v>
+      </c>
+      <c r="AJ227" s="45">
+        <v>0</v>
+      </c>
+      <c r="AK227" s="45">
+        <v>0</v>
+      </c>
+      <c r="AL227" s="23">
+        <v>0</v>
+      </c>
+      <c r="AM227" s="23">
+        <v>0</v>
+      </c>
+      <c r="AN227" s="23">
+        <v>0</v>
+      </c>
+      <c r="AO227" s="23">
+        <v>0</v>
+      </c>
+      <c r="AP227" s="23">
+        <v>0</v>
+      </c>
+      <c r="AQ227" s="23">
+        <v>0</v>
+      </c>
+      <c r="AR227" s="25">
+        <v>0</v>
+      </c>
+      <c r="AS227" s="52">
+        <v>0</v>
+      </c>
+      <c r="AT227" s="50">
+        <v>0</v>
+      </c>
+      <c r="AU227" s="50">
+        <v>0</v>
+      </c>
+      <c r="AV227" s="50">
+        <v>0</v>
+      </c>
+      <c r="AW227" s="38">
+        <v>0</v>
+      </c>
+      <c r="AX227" s="38">
+        <v>0</v>
+      </c>
+      <c r="AY227" s="38">
+        <v>0</v>
+      </c>
+      <c r="AZ227" s="38">
+        <v>0</v>
+      </c>
+      <c r="BA227" s="38">
+        <v>0</v>
+      </c>
+      <c r="BB227" s="38">
+        <v>0</v>
+      </c>
+      <c r="BC227" s="38">
+        <v>0</v>
+      </c>
+      <c r="BD227" s="38">
+        <v>0</v>
+      </c>
+      <c r="BE227" s="38">
+        <v>0</v>
+      </c>
+      <c r="BF227" s="38">
+        <v>0</v>
+      </c>
+      <c r="BG227" s="40">
+        <v>1</v>
+      </c>
+      <c r="BH227" s="40" t="s">
+        <v>2038</v>
+      </c>
+      <c r="BI227" s="40">
         <v>0</v>
       </c>
     </row>
@@ -56701,7 +56892,7 @@
     <row r="2" spans="1:61" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="53">
         <f>MAX(AllEventData!A:A)+1</f>
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2109</v>
@@ -60099,7 +60290,7 @@
         <v>408</v>
       </c>
       <c r="M7">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="s">
         <v>13</v>
@@ -60127,7 +60318,7 @@
       </c>
       <c r="M8">
         <f>J13/M7</f>
-        <v>39.705950435671475</v>
+        <v>33.541019662496844</v>
       </c>
       <c r="N8" t="s">
         <v>2041</v>
@@ -60183,11 +60374,11 @@
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="H11" s="16">
         <f>DEGREES(ATAN(J20/F15))</f>
-        <v>28.178590109959174</v>
+        <v>63.43494882292201</v>
       </c>
       <c r="J11">
         <f>90-H11</f>
-        <v>61.821409890040826</v>
+        <v>26.56505117707799</v>
       </c>
       <c r="N11">
         <v>18980</v>
@@ -60207,7 +60398,7 @@
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="J13" s="16">
         <f>SQRT(F15^2+J20^2)</f>
-        <v>63.529520697074361</v>
+        <v>134.16407864998737</v>
       </c>
       <c r="L13" t="e">
         <f>J13/L12</f>
@@ -60237,13 +60428,13 @@
       </c>
       <c r="F15" s="16">
         <f>F12-F18</f>
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="M16">
         <f>90-H11</f>
-        <v>61.821409890040826</v>
+        <v>26.56505117707799</v>
       </c>
     </row>
     <row r="18" spans="3:14" x14ac:dyDescent="0.25">
@@ -60251,7 +60442,7 @@
         <v>88</v>
       </c>
       <c r="F18" s="15">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="3:14" x14ac:dyDescent="0.25">
@@ -60259,11 +60450,11 @@
         <v>85</v>
       </c>
       <c r="J20" s="15">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="N20">
         <f>8/COS(RADIANS(H11))</f>
-        <v>9.0756458138677658</v>
+        <v>17.888543819998315</v>
       </c>
     </row>
     <row r="21" spans="3:14" x14ac:dyDescent="0.25">

--- a/AllEventData.xlsx
+++ b/AllEventData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\Documents\GitHub\strewnlab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649AEC22-EA8F-4F13-B5E6-88094820B76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2482EB-DF2C-4D4B-959A-8A61C1E25064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9195" yWindow="945" windowWidth="14670" windowHeight="12885" xr2:uid="{C46C341C-A654-450D-9491-A8F495B2F4ED}"/>
+    <workbookView xWindow="1905" yWindow="1485" windowWidth="21600" windowHeight="11385" xr2:uid="{C46C341C-A654-450D-9491-A8F495B2F4ED}"/>
   </bookViews>
   <sheets>
     <sheet name="AllEventData" sheetId="1" r:id="rId1"/>
@@ -209,7 +209,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="2126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3830" uniqueCount="2130">
   <si>
     <t>UTC Date and Time</t>
   </si>
@@ -6588,6 +6588,18 @@
   </si>
   <si>
     <t>Batchewana</t>
+  </si>
+  <si>
+    <t>Fuhai</t>
+  </si>
+  <si>
+    <t>Fuhaizhen</t>
+  </si>
+  <si>
+    <t>Li Weichao</t>
+  </si>
+  <si>
+    <t>Windfall</t>
   </si>
 </sst>
 </file>
@@ -16522,6 +16534,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
@@ -16835,7 +16848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{332638A7-5364-4539-88F3-B010BD503402}">
-  <dimension ref="A1:BI227"/>
+  <dimension ref="A1:BI229"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="6" customWidth="1"/>
@@ -47869,7 +47882,7 @@
         <v>71000</v>
       </c>
       <c r="K195" s="3">
-        <f t="shared" ref="K195:K227" si="17">I195*J195^2/2/4.184/10^12</f>
+        <f t="shared" ref="K195:K229" si="17">I195*J195^2/2/4.184/10^12</f>
         <v>1.2048279158699809E-3</v>
       </c>
       <c r="L195" s="3">
@@ -52779,7 +52792,7 @@
         <v>-6</v>
       </c>
       <c r="H221" s="4">
-        <f t="shared" ref="H221:H227" si="20">F221+G221/24</f>
+        <f t="shared" ref="H221:H229" si="20">F221+G221/24</f>
         <v>45798.115381944444</v>
       </c>
       <c r="I221" s="3">
@@ -52818,7 +52831,7 @@
         <v>5000</v>
       </c>
       <c r="T221" s="3">
-        <f t="shared" ref="T221:T227" si="21">M221</f>
+        <f t="shared" ref="T221:T226" si="21">M221</f>
         <v>69.236000000000004</v>
       </c>
       <c r="U221" s="3">
@@ -53379,7 +53392,7 @@
         <v>27410.59</v>
       </c>
       <c r="R224" s="3">
-        <f>Q224</f>
+        <f t="shared" ref="R224:R229" si="22">Q224</f>
         <v>27410.59</v>
       </c>
       <c r="S224" s="3">
@@ -53569,7 +53582,7 @@
         <v>24686.42</v>
       </c>
       <c r="R225" s="3">
-        <f>Q225</f>
+        <f t="shared" si="22"/>
         <v>24686.42</v>
       </c>
       <c r="S225" s="3">
@@ -53759,7 +53772,7 @@
         <v>32600</v>
       </c>
       <c r="R226" s="3">
-        <f>Q226</f>
+        <f t="shared" si="22"/>
         <v>32600</v>
       </c>
       <c r="S226" s="3">
@@ -53948,7 +53961,7 @@
         <v>20000</v>
       </c>
       <c r="R227" s="3">
-        <f>Q227</f>
+        <f t="shared" si="22"/>
         <v>20000</v>
       </c>
       <c r="S227" s="3">
@@ -54078,6 +54091,383 @@
         <v>2038</v>
       </c>
       <c r="BI227" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A228" s="6">
+        <v>227</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>2126</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>2127</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>1501</v>
+      </c>
+      <c r="E228" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F228" s="17">
+        <v>45962.86041666667</v>
+      </c>
+      <c r="G228" s="21">
+        <v>8</v>
+      </c>
+      <c r="H228" s="4">
+        <f t="shared" si="20"/>
+        <v>45963.193750000006</v>
+      </c>
+      <c r="I228" s="3">
+        <v>500</v>
+      </c>
+      <c r="J228" s="3">
+        <v>20000</v>
+      </c>
+      <c r="K228" s="3">
+        <f t="shared" si="17"/>
+        <v>2.390057361376673E-2</v>
+      </c>
+      <c r="L228" s="3">
+        <v>9.1</v>
+      </c>
+      <c r="M228" s="3">
+        <v>62.5</v>
+      </c>
+      <c r="N228" s="3" t="s">
+        <v>1329</v>
+      </c>
+      <c r="O228" s="3">
+        <v>47.899799999999999</v>
+      </c>
+      <c r="P228" s="3">
+        <v>85.791899999999998</v>
+      </c>
+      <c r="Q228" s="3">
+        <v>27200</v>
+      </c>
+      <c r="R228" s="3">
+        <f t="shared" si="22"/>
+        <v>27200</v>
+      </c>
+      <c r="S228" s="3">
+        <v>8000</v>
+      </c>
+      <c r="T228" s="3">
+        <f>M228</f>
+        <v>62.5</v>
+      </c>
+      <c r="U228" s="3">
+        <v>25000</v>
+      </c>
+      <c r="V228" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="W228" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="X228" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y228" s="3">
+        <v>60000</v>
+      </c>
+      <c r="Z228" s="3">
+        <v>60000</v>
+      </c>
+      <c r="AA228" s="5">
+        <v>4000</v>
+      </c>
+      <c r="AB228" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC228" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD228" s="5">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="AE228" s="5">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="AF228" s="5">
+        <v>500</v>
+      </c>
+      <c r="AG228" s="5">
+        <v>-1</v>
+      </c>
+      <c r="AH228" s="5">
+        <v>1</v>
+      </c>
+      <c r="AI228" s="45">
+        <v>0</v>
+      </c>
+      <c r="AJ228" s="45">
+        <v>0</v>
+      </c>
+      <c r="AK228" s="45">
+        <v>0</v>
+      </c>
+      <c r="AL228" s="23">
+        <v>0</v>
+      </c>
+      <c r="AM228" s="23">
+        <v>0</v>
+      </c>
+      <c r="AN228" s="23">
+        <v>0</v>
+      </c>
+      <c r="AO228" s="23">
+        <v>0</v>
+      </c>
+      <c r="AP228" s="23">
+        <v>0</v>
+      </c>
+      <c r="AQ228" s="23">
+        <v>0</v>
+      </c>
+      <c r="AR228" s="25">
+        <v>0</v>
+      </c>
+      <c r="AS228" s="52">
+        <v>0</v>
+      </c>
+      <c r="AT228" s="50">
+        <v>0</v>
+      </c>
+      <c r="AU228" s="50">
+        <v>0</v>
+      </c>
+      <c r="AV228" s="50">
+        <v>0</v>
+      </c>
+      <c r="AW228" s="38">
+        <v>0</v>
+      </c>
+      <c r="AX228" s="38">
+        <v>0</v>
+      </c>
+      <c r="AY228" s="38">
+        <v>0</v>
+      </c>
+      <c r="AZ228" s="38">
+        <v>0</v>
+      </c>
+      <c r="BA228" s="38">
+        <v>0</v>
+      </c>
+      <c r="BB228" s="38">
+        <v>0</v>
+      </c>
+      <c r="BC228" s="38">
+        <v>0</v>
+      </c>
+      <c r="BD228" s="38">
+        <v>0</v>
+      </c>
+      <c r="BE228" s="38">
+        <v>0</v>
+      </c>
+      <c r="BF228" s="38">
+        <v>0</v>
+      </c>
+      <c r="BG228" s="40">
+        <v>3</v>
+      </c>
+      <c r="BH228" s="40" t="s">
+        <v>2128</v>
+      </c>
+      <c r="BI228" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A229" s="6">
+        <v>228</v>
+      </c>
+      <c r="B229" s="6" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C229" s="6" t="s">
+        <v>2129</v>
+      </c>
+      <c r="D229" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E229" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F229" s="17">
+        <v>46098.539340277777</v>
+      </c>
+      <c r="G229" s="21">
+        <v>-4</v>
+      </c>
+      <c r="H229" s="4">
+        <f t="shared" si="20"/>
+        <v>46098.372673611113</v>
+      </c>
+      <c r="I229" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J229" s="3">
+        <v>17500</v>
+      </c>
+      <c r="K229" s="3">
+        <f t="shared" si="17"/>
+        <v>0.21958652007648186</v>
+      </c>
+      <c r="L229" s="3">
+        <v>157</v>
+      </c>
+      <c r="M229" s="3">
+        <f>77-24.5</f>
+        <v>52.5</v>
+      </c>
+      <c r="N229" s="3" t="s">
+        <v>1329</v>
+      </c>
+      <c r="O229" s="3">
+        <v>41.091320000000003</v>
+      </c>
+      <c r="P229" s="3">
+        <v>-81.923053999999993</v>
+      </c>
+      <c r="Q229" s="3">
+        <v>30000</v>
+      </c>
+      <c r="R229" s="3">
+        <v>30000</v>
+      </c>
+      <c r="S229" s="3">
+        <v>8000</v>
+      </c>
+      <c r="T229" s="3">
+        <v>76</v>
+      </c>
+      <c r="U229" s="3">
+        <v>19800</v>
+      </c>
+      <c r="V229" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="W229" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="X229" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y229" s="3">
+        <v>60000</v>
+      </c>
+      <c r="Z229" s="3">
+        <v>60000</v>
+      </c>
+      <c r="AA229" s="5">
+        <v>300</v>
+      </c>
+      <c r="AB229" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC229" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD229" s="5">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="AE229" s="5">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="AF229" s="5">
+        <v>300</v>
+      </c>
+      <c r="AG229" s="5">
+        <v>-1.5</v>
+      </c>
+      <c r="AH229" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="AI229" s="45">
+        <v>0</v>
+      </c>
+      <c r="AJ229" s="45">
+        <v>0</v>
+      </c>
+      <c r="AK229" s="45">
+        <v>0</v>
+      </c>
+      <c r="AL229" s="23">
+        <v>0</v>
+      </c>
+      <c r="AM229" s="23">
+        <v>0</v>
+      </c>
+      <c r="AN229" s="23">
+        <v>0</v>
+      </c>
+      <c r="AO229" s="23">
+        <v>0</v>
+      </c>
+      <c r="AP229" s="23">
+        <v>0</v>
+      </c>
+      <c r="AQ229" s="23">
+        <v>0</v>
+      </c>
+      <c r="AR229" s="25">
+        <v>0</v>
+      </c>
+      <c r="AS229" s="52">
+        <v>0</v>
+      </c>
+      <c r="AT229" s="50">
+        <v>0</v>
+      </c>
+      <c r="AU229" s="50">
+        <v>0</v>
+      </c>
+      <c r="AV229" s="50">
+        <v>0</v>
+      </c>
+      <c r="AW229" s="38">
+        <v>0</v>
+      </c>
+      <c r="AX229" s="38">
+        <v>0</v>
+      </c>
+      <c r="AY229" s="38">
+        <v>0</v>
+      </c>
+      <c r="AZ229" s="38">
+        <v>0</v>
+      </c>
+      <c r="BA229" s="38">
+        <v>0</v>
+      </c>
+      <c r="BB229" s="38">
+        <v>0</v>
+      </c>
+      <c r="BC229" s="38">
+        <v>0</v>
+      </c>
+      <c r="BD229" s="38">
+        <v>0</v>
+      </c>
+      <c r="BE229" s="38">
+        <v>0</v>
+      </c>
+      <c r="BF229" s="38">
+        <v>0</v>
+      </c>
+      <c r="BG229" s="40">
+        <v>1</v>
+      </c>
+      <c r="BH229" s="40" t="s">
+        <v>2038</v>
+      </c>
+      <c r="BI229" s="40">
         <v>0</v>
       </c>
     </row>
@@ -56892,7 +57282,7 @@
     <row r="2" spans="1:61" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="53">
         <f>MAX(AllEventData!A:A)+1</f>
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2109</v>
@@ -60290,7 +60680,7 @@
         <v>408</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="s">
         <v>13</v>
@@ -60318,7 +60708,7 @@
       </c>
       <c r="M8">
         <f>J13/M7</f>
-        <v>33.541019662496844</v>
+        <v>8.5534268636091753</v>
       </c>
       <c r="N8" t="s">
         <v>2041</v>
@@ -60374,11 +60764,11 @@
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="H11" s="16">
         <f>DEGREES(ATAN(J20/F15))</f>
-        <v>63.43494882292201</v>
+        <v>76.017911316998934</v>
       </c>
       <c r="J11">
         <f>90-H11</f>
-        <v>26.56505117707799</v>
+        <v>13.982088683001066</v>
       </c>
       <c r="N11">
         <v>18980</v>
@@ -60389,7 +60779,7 @@
         <v>89</v>
       </c>
       <c r="F12" s="15">
-        <v>80</v>
+        <v>25.7</v>
       </c>
       <c r="N12">
         <v>15540</v>
@@ -60398,7 +60788,7 @@
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="J13" s="16">
         <f>SQRT(F15^2+J20^2)</f>
-        <v>134.16407864998737</v>
+        <v>25.660280590827526</v>
       </c>
       <c r="L13" t="e">
         <f>J13/L12</f>
@@ -60428,13 +60818,13 @@
       </c>
       <c r="F15" s="16">
         <f>F12-F18</f>
-        <v>60</v>
+        <v>6.1999999999999993</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="M16">
         <f>90-H11</f>
-        <v>26.56505117707799</v>
+        <v>13.982088683001066</v>
       </c>
     </row>
     <row r="18" spans="3:14" x14ac:dyDescent="0.25">
@@ -60442,7 +60832,7 @@
         <v>88</v>
       </c>
       <c r="F18" s="15">
-        <v>20</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="20" spans="3:14" x14ac:dyDescent="0.25">
@@ -60450,11 +60840,11 @@
         <v>85</v>
       </c>
       <c r="J20" s="15">
-        <v>120</v>
+        <v>24.9</v>
       </c>
       <c r="N20">
         <f>8/COS(RADIANS(H11))</f>
-        <v>17.888543819998315</v>
+        <v>33.110039472035524</v>
       </c>
     </row>
     <row r="21" spans="3:14" x14ac:dyDescent="0.25">
